--- a/TESTER/LAB 3.xlsx
+++ b/TESTER/LAB 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TESTER\DangVanKhoa\TESTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5A2E4E-E947-4D65-82F6-E96C350317D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA54722-55BB-472E-A43B-2A8B982BF8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{48A1202D-E04B-4B0C-B498-FBDC25FE4C5B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{48A1202D-E04B-4B0C-B498-FBDC25FE4C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bài 1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="254">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -861,6 +861,105 @@
   <si>
     <t>Username: 'user123'
 Password: 'password10'</t>
+  </si>
+  <si>
+    <t>Kiểm thử ngày nằm giữa khoảng (28) - Giảm 70%</t>
+  </si>
+  <si>
+    <t>Bước 1: Truy cập trang Lazada SaleBước 2: Nhập ngày = 28Bước 3: Click Nhận coupon</t>
+  </si>
+  <si>
+    <t>Ngày: 28</t>
+  </si>
+  <si>
+    <t>Kiểm thử để trống trường nhập</t>
+  </si>
+  <si>
+    <t>Bước 1: Truy cập trang Lazada SaleBước 2: Để trống ô nhập ngàyBước 3: Click Nhận coupon</t>
+  </si>
+  <si>
+    <t>Ngày: (Để trống)</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi: 'Vui lòng nhập ngày'</t>
+  </si>
+  <si>
+    <t>Kiểm thử nhập ký tự không phải số</t>
+  </si>
+  <si>
+    <t>Bước 1: Truy cập trang Lazada SaleBước 2: Nhập ký tự chữ hoặc đặc biệtBước 3: Click Nhận coupon</t>
+  </si>
+  <si>
+    <t>Ngày: "abc" hoặc "@#$"</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi: 'Định dạng không hợp lệ'</t>
+  </si>
+  <si>
+    <t>Kiểm thử để trống Username và Password</t>
+  </si>
+  <si>
+    <t>Bước 1: Truy cập trang đăng nhậpBước 2: Để trống ô UsernameBước 3: Để trống ô PasswordBước 4: Click Login</t>
+  </si>
+  <si>
+    <t>Username: (Để trống)Password: (Để trống)</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi: "Vui lòng nhập Username/Password"</t>
+  </si>
+  <si>
+    <t>Kiểm thử đăng nhập với Password sai</t>
+  </si>
+  <si>
+    <t>Bước 1: Truy cập trang đăng nhậpBước 2: Nhập Username hợp lệBước 3: Nhập Password saiBước 4: Click Login</t>
+  </si>
+  <si>
+    <t>Username: 'user123'Password: 'wrongpass'</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi: "Sai tên đăng nhập hoặc mật khẩu"</t>
+  </si>
+  <si>
+    <t>Kiểm thử để trống trường dữ liệu</t>
+  </si>
+  <si>
+    <t>Bước 1: Truy cập trang đăng nhậpBước 2: Để trống Username/PasswordBước 3: Click Login</t>
+  </si>
+  <si>
+    <t>Username: (Trống)Password: (Trống)</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo: "Vui lòng nhập đầy đủ thông tin"</t>
+  </si>
+  <si>
+    <t>Kiểm thử mật khẩu sai định dạng (chứa khoảng trắng)</t>
+  </si>
+  <si>
+    <t>Bước 1: Truy cập trang đăng nhậpBước 2: Nhập Username hợp lệBước 3: Nhập Password có khoảng trắngBước 4: Click Login</t>
+  </si>
+  <si>
+    <t>Username: 'user123'Password: 'pass 123'</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi: "Tên đăng nhập hoặc mật khẩu không đúng"</t>
+  </si>
+  <si>
+    <t>Kiểm thử đăng nhập thành công</t>
+  </si>
+  <si>
+    <t>Bước 1: Truy cập trang đăng nhậpBước 2: Nhập Username hợp lệ (6-20 ký tự)Bước 3: Nhập Password hợp lệ (&gt;=6 ký tự)Bước 4: Click Login</t>
+  </si>
+  <si>
+    <t>Username: 'user123'Password: 'pass123'</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công</t>
+  </si>
+  <si>
+    <t>Kiểm thử mật khẩu không chính xác</t>
+  </si>
+  <si>
+    <t>Hiển thị lỗi: "Sai mật khẩu"</t>
   </si>
 </sst>
 </file>
@@ -890,7 +989,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -898,16 +997,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1464,8 +1581,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C99993E-2B5E-4F1B-9DFB-B49F33A6E3CC}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1628,7 +1753,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="138" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -1648,6 +1773,52 @@
         <v>12</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="111" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1658,7 +1829,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D9E7C06-2B18-4E16-9275-E57C464C9C92}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1776,7 +1947,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="193.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -1796,6 +1967,52 @@
         <v>12</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="235.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1807,7 +2024,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22FA456A-ED16-471F-8580-CFECDC43C5EE}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1971,7 +2188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="151.80000000000001" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -1991,6 +2208,52 @@
         <v>12</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="166.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="221.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2001,7 +2264,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72DB0AF-D488-4703-BAEE-A0A3B3F3A595}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -2165,7 +2428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="151.80000000000001" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -2185,6 +2448,52 @@
         <v>12</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="207.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="193.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2435,8 +2744,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE10DF4-9769-49AB-97D3-6C619DD58FB1}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2576,7 +2888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="179.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="180" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
@@ -2599,8 +2911,78 @@
         <v>13</v>
       </c>
     </row>
+    <row r="8" spans="1:7" ht="97.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
